--- a/API/Utils/Templates/BookInsert.xlsx
+++ b/API/Utils/Templates/BookInsert.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30502"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30516"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC446684-0F6C-4278-8AF6-9DB73F94292A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{50D9E06A-A795-40CD-ACE9-96EACA6FBBFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Title</t>
   </si>
@@ -61,12 +61,6 @@
   </si>
   <si>
     <t>WritingStatus</t>
-  </si>
-  <si>
-    <t>Author</t>
-  </si>
-  <si>
-    <t>Author2</t>
   </si>
   <si>
     <t>Url</t>
@@ -82,7 +76,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -94,6 +91,20 @@
       <u/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFF1FA8C"/>
+      <name val="Consolas"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -116,14 +127,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -436,10 +453,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="24.5703125" customWidth="1"/>
+    <col min="2" max="2" width="31.140625" customWidth="1"/>
+    <col min="5" max="5" width="21.5703125" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" customWidth="1"/>
+    <col min="8" max="8" width="31" customWidth="1"/>
+    <col min="9" max="9" width="40.42578125" customWidth="1"/>
+    <col min="10" max="10" width="24.5703125" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -476,15 +503,81 @@
       <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="N2" s="1"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="D2" s="2"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="4"/>
+      <c r="J2" s="5"/>
+      <c r="L2" s="1"/>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="D3" s="2"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="4"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="D4" s="2"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="4"/>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="D5" s="2"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="4"/>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="D6" s="2"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="D7" s="2"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="4"/>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="D8" s="2"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="4"/>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="D9" s="2"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="4"/>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="D10" s="2"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="4"/>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="D11" s="2"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="4"/>
+    </row>
+    <row r="17" spans="7:7">
+      <c r="G17" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
